--- a/LoanOfficer-A/2023/100 renita.xlsx
+++ b/LoanOfficer-A/2023/100 renita.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4200</v>
+        <v>7800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>19800</v>
+        <v>16200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45768</v>
+      </c>
+      <c r="G3" s="4">
+        <v>200</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -906,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45768</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -938,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45768</v>
+      </c>
+      <c r="G5" s="4">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -970,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45768</v>
+      </c>
+      <c r="G6" s="4">
+        <v>200</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1002,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45768</v>
+      </c>
+      <c r="G7" s="4">
+        <v>200</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1034,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45770</v>
+      </c>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1066,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45771</v>
+      </c>
+      <c r="G9" s="4">
+        <v>200</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1098,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45773</v>
+      </c>
+      <c r="G10" s="4">
+        <v>200</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1130,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45774</v>
+      </c>
+      <c r="G11" s="4">
+        <v>200</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1534,9 +1588,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45767</v>
+      </c>
+      <c r="C24" s="4">
+        <v>200</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1560,9 +1620,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45767</v>
+      </c>
+      <c r="C25" s="4">
+        <v>200</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1586,9 +1652,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45767</v>
+      </c>
+      <c r="C26" s="4">
+        <v>200</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1612,9 +1684,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45767</v>
+      </c>
+      <c r="C27" s="4">
+        <v>200</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1638,9 +1716,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45768</v>
+      </c>
+      <c r="C28" s="4">
+        <v>200</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1664,9 +1748,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45768</v>
+      </c>
+      <c r="C29" s="4">
+        <v>200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1690,9 +1780,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45768</v>
+      </c>
+      <c r="C30" s="4">
+        <v>200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1716,9 +1812,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45768</v>
+      </c>
+      <c r="C31" s="4">
+        <v>200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1742,9 +1844,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45768</v>
+      </c>
+      <c r="C32" s="4">
+        <v>200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/100 renita.xlsx
+++ b/LoanOfficer-A/2023/100 renita.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7800</v>
+        <v>8800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>16200</v>
+        <v>15200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1216,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45785</v>
+      </c>
+      <c r="G12" s="4">
+        <v>200</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1248,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45785</v>
+      </c>
+      <c r="G13" s="4">
+        <v>200</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1280,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45788</v>
+      </c>
+      <c r="G14" s="4">
+        <v>200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1312,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45788</v>
+      </c>
+      <c r="G15" s="4">
+        <v>200</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1344,9 +1368,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45788</v>
+      </c>
+      <c r="G16" s="4">
+        <v>200</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>

--- a/LoanOfficer-A/2023/100 renita.xlsx
+++ b/LoanOfficer-A/2023/100 renita.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD10000.1-OCT'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8800</v>
+        <v>9800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>15200</v>
+        <v>14200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1406,9 +1406,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45808</v>
+      </c>
+      <c r="G17" s="4">
+        <v>200</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1438,9 +1444,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45808</v>
+      </c>
+      <c r="G18" s="4">
+        <v>200</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1470,9 +1482,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45808</v>
+      </c>
+      <c r="G19" s="4">
+        <v>200</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1502,9 +1520,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45808</v>
+      </c>
+      <c r="G20" s="4">
+        <v>200</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1534,9 +1558,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45808</v>
+      </c>
+      <c r="G21" s="4">
+        <v>200</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>

--- a/LoanOfficer-A/2023/100 renita.xlsx
+++ b/LoanOfficer-A/2023/100 renita.xlsx
@@ -393,7 +393,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -428,7 +428,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9800</v>
+        <v>10800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>14200</v>
+        <v>13200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1596,9 +1596,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45854</v>
+      </c>
+      <c r="G22" s="4">
+        <v>200</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1628,9 +1634,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45860</v>
+      </c>
+      <c r="G23" s="4">
+        <v>200</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1660,9 +1672,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45860</v>
+      </c>
+      <c r="G24" s="4">
+        <v>200</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1692,9 +1710,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45860</v>
+      </c>
+      <c r="G25" s="4">
+        <v>200</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1724,9 +1748,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45860</v>
+      </c>
+      <c r="G26" s="4">
+        <v>200</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
